--- a/data/trans_orig/IP1007-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86599</t>
+          <t>86603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82765</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171780</t>
+          <t>171514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177076</t>
+          <t>177072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,47 +1110,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5711</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>551</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5477</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471514</t>
+          <t>471280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476440</t>
+          <t>476439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887134</t>
+          <t>887938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892525</t>
+          <t>892527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>170904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329294</t>
+          <t>329305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676304</t>
+          <t>675877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680497</t>
+          <t>680498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713952</t>
+          <t>714490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720688</t>
+          <t>720715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393735</t>
+          <t>1393685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400711</t>
+          <t>1400664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444466</t>
+          <t>443998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489175</t>
+          <t>488441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937222</t>
+          <t>936679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3026,92 +3026,92 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
           <t>2851</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162489</t>
+          <t>162503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333850</t>
+          <t>334050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701920</t>
+          <t>701444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744016</t>
+          <t>744053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447719</t>
+          <t>1447685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453859</t>
+          <t>1453858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466430</t>
+          <t>465968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484307</t>
+          <t>484439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953575</t>
+          <t>953881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960398</t>
+          <t>960400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184601</t>
+          <t>184029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356501</t>
+          <t>356001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698116</t>
+          <t>698555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738921</t>
+          <t>739007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744216</t>
+          <t>744220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1441715</t>
+          <t>1441690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448058</t>
+          <t>1448057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1007-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1214</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4264</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85502</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82135</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89653</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86603</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85502</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82716</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>262</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171514</t>
+          <t>171812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177072</t>
+          <t>177077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5711</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>471538</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476440</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475066</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471280</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476439</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1344</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887938</t>
+          <t>888103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892527</t>
+          <t>892525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3162</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173542</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>170904</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>171418</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329305</t>
+          <t>329898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7484</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>718706</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714566</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720717</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679283</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>675877</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680498</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>675523</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>680497</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>718706</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>714490</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720715</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2095</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393685</t>
+          <t>1393699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400664</t>
+          <t>1401060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2438,47 +2438,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2673,102 +2673,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5702</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3963</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5578</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5424</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>491717</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>488618</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448804</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443998</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>445205</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491717</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>488441</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1354</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936679</t>
+          <t>936525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,92 +3011,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164772</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162503</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>161894</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334050</t>
+          <t>334037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5484</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3448</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746814</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>743926</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705464</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>701444</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>701306</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>746814</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>744053</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447685</t>
+          <t>1448680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453858</t>
+          <t>1453861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6322</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5817</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>487473</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484916</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>471127</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>465968</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>466473</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487473</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>484439</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1406</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953881</t>
+          <t>953971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960400</t>
+          <t>960398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4055</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>692</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4196</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186803</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183440</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186803</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>184029</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>528</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356001</t>
+          <t>356432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,74 +4957,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5837</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742891</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>739520</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744222</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>703208</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698555</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698551</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742891</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739007</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744220</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2122</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1441690</t>
+          <t>1441294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448057</t>
+          <t>1448519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
